--- a/Revision/20260609/0609_missingness_indicator_key_features_regression_with_p.xlsx
+++ b/Revision/20260609/0609_missingness_indicator_key_features_regression_with_p.xlsx
@@ -716,10 +716,10 @@
         <v>23901</v>
       </c>
       <c r="E5" t="n">
-        <v>23901</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -970,10 +970,10 @@
         <v>6216</v>
       </c>
       <c r="E9" t="n">
-        <v>6216</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
